--- a/data/S1969_70_FINAL.xlsx
+++ b/data/S1969_70_FINAL.xlsx
@@ -28,8 +28,11 @@
     <sheet name="SERIES" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="CLUBS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="META" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -37,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +55,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +82,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,12 +100,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19647,7 +19665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19696,6 +19714,57 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0017</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1969_70_0017 'Kvalifikace o ČNHL' (L25, parent=NODE_S1969_70_0010) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0021</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1969_70_0021 'KVAL skupina A' (L25, parent=NODE_S1969_70_0020) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0022</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1969_70_0022 'KVAL skupina B' (L25, parent=NODE_S1969_70_0020) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -56651,6 +56720,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0017</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1969_70_0017 'Kvalifikace o ČNHL' (L25, parent=NODE_S1969_70_0010) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0021</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1969_70_0021 'KVAL skupina A' (L25, parent=NODE_S1969_70_0020) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0022</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1969_70_0022 'KVAL skupina B' (L25, parent=NODE_S1969_70_0020) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1969_70_FINAL.xlsx
+++ b/data/S1969_70_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19665,7 +19665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19718,14 +19718,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NODE_S1969_70_0017</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1969_70_0017 'Kvalifikace o ČNHL' (L25, parent=NODE_S1969_70_0010) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -19735,14 +19730,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1969_70_0021</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1969_70_0021 'KVAL skupina A' (L25, parent=NODE_S1969_70_0020) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19752,17 +19742,252 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1969_70_0022</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1969_70_0022 'KVAL skupina B' (L25, parent=NODE_S1969_70_0020) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1968_69_0016 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -29326,12 +29551,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29452,12 +29677,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -29583,12 +29808,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -30883,12 +31108,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -30972,12 +31197,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -31286,12 +31511,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -31333,12 +31558,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -31568,12 +31793,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -31615,12 +31840,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -31845,12 +32070,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -32033,12 +32258,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Litoměřice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -36458,12 +36683,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -38013,12 +38238,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -38060,12 +38285,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38886,12 +39111,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá. || TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Sm. Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -39633,12 +39858,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -47270,12 +47495,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -47495,12 +47720,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Hradec Králové = Vysokoškolská TJ Hradec (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Vysokoskolsky klub (Univerzita Hradec Králové, dnes UHK). city Hradec Králové.</t>
+          <t>Hradec Králové = Vysokoškolská TJ Hradec (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Vysokoskolsky klub (Univerzita Hradec Králové, dnes UHK). city Hradec Králové. || TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Vysokoškolská TJ Hradec</t>
+          <t>Hradec</t>
         </is>
       </c>
     </row>
@@ -50087,12 +50312,12 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -50527,12 +50752,12 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>Vranov nad Dyjí</t>
+          <t>Rudá Hvězda</t>
         </is>
       </c>
     </row>
@@ -52000,12 +52225,12 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -56726,11 +56951,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -56775,21 +57000,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1969_70_0017</t>
+          <t>CLUB_S1969_70_0011</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1969_70_0017 'Kvalifikace o ČNHL' (L25, parent=NODE_S1969_70_0010) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -56797,21 +57020,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1969_70_0021</t>
+          <t>CLUB_S1969_70_0014</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1969_70_0021 'KVAL skupina A' (L25, parent=NODE_S1969_70_0020) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -56819,24 +57040,422 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1969_70_0022</t>
+          <t>CLUB_S1969_70_0017</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1969_70_0022 'KVAL skupina B' (L25, parent=NODE_S1969_70_0020) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0024</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1968_69_0016 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0047</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0049</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0056</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0057</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0062</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0063</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0068</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0072</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0177</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0213</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0214</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0232</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0248</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0421</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0426</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0483</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0493</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0517</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1969_70_0528</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1969_70_FINAL.xlsx
+++ b/data/S1969_70_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19665,7 +19665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19720,7 +19720,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1968_69_0016 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19744,7 +19744,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1968_69_0016 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19768,7 +19768,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19792,7 +19792,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19816,7 +19816,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19840,7 +19840,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19864,130 +19864,10 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -20004,7 +19884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20063,6 +19943,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20105,6 +19990,11 @@
           <t>10 týmů, jeden stůl. Mistr: Dukla Jihlava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20152,6 +20042,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20320,6 +20215,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20362,6 +20262,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20404,6 +20309,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20792,6 +20702,11 @@
           <t>VTJ Dukla Letec Hradec Králové po sezoně ukončila činnost. TJ Spartak Třebíč postoupil do ČNHL přímo. TJ Sigma MŽ Olomouc se přímého postupu do ČNHL vzdala.</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0014</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21049,6 +20964,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0018</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -21175,6 +21095,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -21217,6 +21142,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0024</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -21343,6 +21273,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0027</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -21847,6 +21782,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0038</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -21889,6 +21829,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0039</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -21973,6 +21918,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0041</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -22015,6 +21965,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0042</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -22104,6 +22059,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0045</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22146,6 +22106,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0046</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -22356,6 +22321,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0048</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -22398,6 +22368,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0049</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -22440,6 +22415,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0050</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22482,6 +22462,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0051</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22529,6 +22514,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0053</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -22571,6 +22561,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0054</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -22613,6 +22608,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0055</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -22655,6 +22655,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0059</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -22697,6 +22702,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0060</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -22739,6 +22749,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0061</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22781,6 +22796,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0062</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -22823,6 +22843,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0063</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22865,6 +22890,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0064</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -22949,6 +22979,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0066</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -22991,6 +23026,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0067</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -23033,6 +23073,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0068</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -23421,6 +23466,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0075</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -23463,6 +23513,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0076</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -23799,6 +23854,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0085</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -23839,6 +23899,11 @@
       <c r="K90" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1968_69_0086</t>
         </is>
       </c>
     </row>
@@ -29551,12 +29616,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29677,12 +29742,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -29808,12 +29873,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -31108,12 +31173,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -31197,12 +31262,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -32070,12 +32135,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -32258,12 +32323,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice. || TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Litoměřice (Wiki D42 - registr ustavy 04/2026). Vojensky klub - HC Stadion Litoměřice (dnes). POSTUP do 1.ligy 1961/62. city Litoměřice.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Litoměřice</t>
         </is>
       </c>
     </row>
@@ -47495,12 +47560,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -50752,12 +50817,12 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí. || TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Vranov nL Dyjí = TJ Rudá Hvězda Vranov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Znojmo). **Vranov nL Dyjí** = lazenske/turisticke mesto, **zámek Vranov nL Dyjí** (barokní pamatka), vodni prehrada (Vranovska prehrada - tzv. 'Moravsky moře'). RH = Ruda hvezda (SNB). NE Vranov nad Topľou (SVK)! city Vranov nad Dyjí.</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>Rudá Hvězda</t>
+          <t>Vranov nad Dyjí</t>
         </is>
       </c>
     </row>
@@ -52225,12 +52290,12 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -56951,7 +57016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57005,12 +57070,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0011</t>
+          <t>CLUB_S1969_70_0024</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1968_69_0016 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -57025,12 +57090,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0014</t>
+          <t>CLUB_S1969_70_0056</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57045,12 +57110,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0017</t>
+          <t>CLUB_S1969_70_0057</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57065,12 +57130,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0024</t>
+          <t>CLUB_S1969_70_0062</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1968_69_0016 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57085,12 +57150,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0047</t>
+          <t>CLUB_S1969_70_0063</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57105,12 +57170,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0049</t>
+          <t>CLUB_S1969_70_0177</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57125,12 +57190,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0056</t>
+          <t>CLUB_S1969_70_0213</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57145,12 +57210,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0057</t>
+          <t>CLUB_S1969_70_0214</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57165,12 +57230,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0062</t>
+          <t>CLUB_S1969_70_0232</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57185,12 +57250,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0063</t>
+          <t>CLUB_S1969_70_0248</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57205,12 +57270,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0068</t>
+          <t>CLUB_S1969_70_0426</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57225,12 +57290,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0072</t>
+          <t>CLUB_S1969_70_0483</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Litoměřice' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57245,217 +57310,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0177</t>
+          <t>CLUB_S1969_70_0517</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0213</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0214</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0232</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0248</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0421</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0426</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0483</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0493</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Vranov nad Dyjí' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0517</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S1969_70_0528</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F24"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1969_70_FINAL.xlsx
+++ b/data/S1969_70_FINAL.xlsx
@@ -31,7 +31,7 @@
     <sheet name="TODO" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TODO'!$A$1:$F$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19665,7 +19665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19718,45 +19718,60 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>KVAL</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1968_69_0016 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[club-fate] TJ Sokol Losiná odstoupil; skupina B už nebyla dohrávána. (club_id: CLUB_S1969_70_0279)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[club-fate] Sokol Čimice — odstoupili</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[club-fate] RH Strašnice — odstoupili</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1968_69_0016 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19768,7 +19783,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19780,7 +19795,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19792,7 +19807,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19804,7 +19819,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19816,7 +19831,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19828,7 +19843,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19840,7 +19855,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19852,7 +19867,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19864,10 +19879,58 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'TJ Sokol Losiná odstoupil; skupina B už nebyla dohrávána.' [fix_club_notes_in_block_name]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -41385,7 +41448,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Losiná = Sokol Losiná (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj (okres Plzen-jih). city Losiná.</t>
+          <t>Losiná = Sokol Losiná (Wiki D42 - registr ustavy 04/2026). Zapadocesky/Plzensky kraj (okres Plzen-jih). city Losiná. || TBD: extrahováno z block_name: 'TJ Sokol Losiná odstoupil; skupina B už nebyla dohrávána.' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -57016,7 +57079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -57270,12 +57333,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0426</t>
+          <t>CLUB_S1969_70_0279</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: extrahováno z block_name: 'TJ Sokol Losiná odstoupil; skupina B už nebyla dohrávána.' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -57290,12 +57353,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1969_70_0483</t>
+          <t>CLUB_S1969_70_0426</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vysokoškolská TJ Hradec' → 'Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -57310,17 +57373,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>CLUB_S1969_70_0483</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>CLUB_S1969_70_0517</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -63386,7 +63469,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Kvalifikace o divizi / skupina B / TJ Sokol Losiná odstoupil; skupina B už nebyla dohrávána.</t>
+          <t>Kvalifikace o divizi / skupina B</t>
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
@@ -65141,7 +65224,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>II.třída / Sokol Čimice — odstoupili</t>
+          <t>II.třída</t>
         </is>
       </c>
       <c r="C14" s="2" t="n"/>
@@ -65174,7 +65257,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>II.třída / RH Strašnice — odstoupili</t>
+          <t>II.třída</t>
         </is>
       </c>
       <c r="C15" s="2" t="n"/>

--- a/data/S1969_70_FINAL.xlsx
+++ b/data/S1969_70_FINAL.xlsx
@@ -29109,7 +29109,7 @@
         <v>138</v>
       </c>
       <c r="M43" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -57762,7 +57762,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="M5" t="n">
         <v>23</v>
@@ -58956,7 +58956,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
@@ -59159,7 +59159,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="M23" t="n">
         <v>19</v>

--- a/data/S1969_70_FINAL.xlsx
+++ b/data/S1969_70_FINAL.xlsx
@@ -19947,7 +19947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20009,6 +20009,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1969_70_FINAL.xlsx
+++ b/data/S1969_70_FINAL.xlsx
@@ -20278,6 +20278,16 @@
           <t>NODE_S1969_70_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1969_70_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20292,6 +20302,14 @@
         <is>
           <t>NODE_S1968_69_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -20325,6 +20343,8 @@
           <t>NODE_S1969_70_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20339,6 +20359,14 @@
         <is>
           <t>NODE_S1968_69_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -20372,6 +20400,8 @@
           <t>NODE_S1969_70_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20386,6 +20416,14 @@
         <is>
           <t>NODE_S1968_69_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -21336,6 +21374,8 @@
           <t>NODE_S1969_70_0026</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21350,6 +21390,14 @@
         <is>
           <t>NODE_S1968_69_0027</t>
         </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -22300,6 +22348,8 @@
           <t>NODE_S1969_70_0048</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22309,6 +22359,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -23136,6 +23194,8 @@
           <t>NODE_S1969_70_0066</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23150,6 +23210,14 @@
         <is>
           <t>NODE_S1968_69_0068</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -24179,6 +24247,8 @@
           <t>NODE_S1969_70_0090</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24188,6 +24258,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="96">

--- a/data/S1969_70_FINAL.xlsx
+++ b/data/S1969_70_FINAL.xlsx
@@ -720,6 +720,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
@@ -20343,8 +20348,6 @@
           <t>NODE_S1969_70_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20400,8 +20403,6 @@
           <t>NODE_S1969_70_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21374,8 +21375,6 @@
           <t>NODE_S1969_70_0026</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22348,8 +22347,6 @@
           <t>NODE_S1969_70_0048</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23194,8 +23191,6 @@
           <t>NODE_S1969_70_0066</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24247,8 +24242,6 @@
           <t>NODE_S1969_70_0090</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -56889,7 +56882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57153,6 +57146,18 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>Kvalifikace o divizi sk. B po odstoupení TJ Sokol Losiná už nebyla dohrávána.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>
